--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128051765</v>
       </c>
       <c r="B2" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128051763</v>
       </c>
       <c r="B3" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128051880</v>
       </c>
       <c r="B4" t="n">
-        <v>98512</v>
+        <v>98605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,6 +974,107 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128504874</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92149</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Aftersberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>408594</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6666192</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128051765</v>
       </c>
       <c r="B2" t="n">
-        <v>100660</v>
+        <v>100674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128051763</v>
       </c>
       <c r="B3" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128051880</v>
       </c>
       <c r="B4" t="n">
-        <v>98605</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128504874</v>
       </c>
       <c r="B5" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128051765</v>
+        <v>128504874</v>
       </c>
       <c r="B2" t="n">
-        <v>100674</v>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408526</v>
+        <v>408594</v>
       </c>
       <c r="R2" t="n">
-        <v>6666151</v>
+        <v>6666192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +779,7 @@
         <v>128051763</v>
       </c>
       <c r="B3" t="n">
-        <v>91429</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128051880</v>
+        <v>128051767</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>80467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,38 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Aftersberget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408576</v>
+        <v>408676</v>
       </c>
       <c r="R4" t="n">
-        <v>6666217</v>
+        <v>6666325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -976,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128504874</v>
+        <v>128051768</v>
       </c>
       <c r="B5" t="n">
-        <v>92218</v>
+        <v>99153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,37 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Aftersberget, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408594</v>
+        <v>408683</v>
       </c>
       <c r="R5" t="n">
-        <v>6666192</v>
+        <v>6666335</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,12 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1058,7 +1049,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1074,6 +1064,210 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128051880</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Aftersberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>408576</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6666217</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128051765</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Aftersberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>408526</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6666151</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44506-2025 artfynd.xlsx
+++ b/artfynd/A 44506-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504874</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128051763</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128051767</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128051768</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128051880</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,8 +1298,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128051765</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>